--- a/B8 Fiducial - k_eff - Sensitivity Analyses/B8_results.xlsx
+++ b/B8 Fiducial - k_eff - Sensitivity Analyses/B8_results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MCNP\haigerloch\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\MCNP\b8\B8 Fiducial - k_eff - Sensitivity Analyses\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E636B2A-B69F-4253-A2A4-9DC4DDEB09A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{621A22DB-D118-48B4-A527-8BCF8030EAC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="17496" activeTab="1" xr2:uid="{DC12915E-B1A7-564D-949D-4967E0B731EC}"/>
   </bookViews>
@@ -5529,7 +5529,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A33" s="11" t="s">
         <v>24</v>
       </c>
@@ -5599,7 +5599,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A34" s="11" t="s">
         <v>24</v>
       </c>
@@ -5669,7 +5669,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A35" s="11" t="s">
         <v>24</v>
       </c>
@@ -5739,7 +5739,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A36" s="11" t="s">
         <v>24</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A37" s="11" t="s">
         <v>24</v>
       </c>
@@ -5878,8 +5878,9 @@
       <c r="V37" s="1" t="s">
         <v>70</v>
       </c>
+      <c r="Y37" s="1"/>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.3">
       <c r="A38" s="11" t="s">
         <v>24</v>
       </c>
@@ -5949,7 +5950,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B39" s="1"/>
       <c r="C39" s="1"/>
       <c r="D39" s="33"/>
@@ -5961,7 +5962,7 @@
       <c r="J39" s="3"/>
       <c r="K39" s="33"/>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.3">
       <c r="B40" s="1"/>
       <c r="C40" s="1"/>
       <c r="D40" s="33"/>
